--- a/Models/КРС/results/КРС - Результаты прогнозов ХВ средние.xlsx
+++ b/Models/КРС/results/КРС - Результаты прогнозов ХВ средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>153.57</v>
+        <v>229.47</v>
       </c>
       <c r="C2" t="n">
-        <v>129.92</v>
+        <v>193.56</v>
       </c>
       <c r="D2" t="n">
-        <v>4.77</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>778.2</v>
+        <v>319.78</v>
       </c>
       <c r="C3" t="n">
-        <v>600.08</v>
+        <v>243.58</v>
       </c>
       <c r="D3" t="n">
-        <v>10.54</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1064.41</v>
+        <v>903.49</v>
       </c>
       <c r="C4" t="n">
-        <v>880.87</v>
+        <v>750</v>
       </c>
       <c r="D4" t="n">
-        <v>12.93</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>169.73</v>
+        <v>142.42</v>
       </c>
       <c r="C5" t="n">
-        <v>148.49</v>
+        <v>126.22</v>
       </c>
       <c r="D5" t="n">
-        <v>8.869999999999999</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>414.51</v>
+        <v>388.38</v>
       </c>
       <c r="C6" t="n">
-        <v>357.77</v>
+        <v>318.35</v>
       </c>
       <c r="D6" t="n">
-        <v>9.460000000000001</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="7">
@@ -537,14 +537,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.84</v>
+        <v>11.11</v>
       </c>
       <c r="C7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100.69</v>
-      </c>
+        <v>8.56</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,13 +551,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232.3</v>
+        <v>183.5</v>
       </c>
       <c r="C9" t="n">
-        <v>203.83</v>
+        <v>164.1</v>
       </c>
       <c r="D9" t="n">
-        <v>43.1</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +583,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>497.74</v>
+        <v>746.6</v>
       </c>
       <c r="C10" t="n">
-        <v>430.01</v>
+        <v>597.03</v>
       </c>
       <c r="D10" t="n">
-        <v>10.74</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +599,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>260.95</v>
+        <v>233.15</v>
       </c>
       <c r="C11" t="n">
-        <v>218.99</v>
+        <v>188.09</v>
       </c>
       <c r="D11" t="n">
-        <v>5.22</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +615,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>202.69</v>
+        <v>121.84</v>
       </c>
       <c r="C12" t="n">
-        <v>181.67</v>
+        <v>102.56</v>
       </c>
       <c r="D12" t="n">
-        <v>6.67</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +631,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>866.0599999999999</v>
+        <v>451.46</v>
       </c>
       <c r="C13" t="n">
-        <v>650.65</v>
+        <v>394.44</v>
       </c>
       <c r="D13" t="n">
-        <v>14.93</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +647,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>121.53</v>
+        <v>172.81</v>
       </c>
       <c r="C14" t="n">
-        <v>103.69</v>
+        <v>135.73</v>
       </c>
       <c r="D14" t="n">
-        <v>7.31</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +663,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56.08</v>
+        <v>63.19</v>
       </c>
       <c r="C15" t="n">
-        <v>41.9</v>
+        <v>48.95</v>
       </c>
       <c r="D15" t="n">
-        <v>22.3</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +679,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>341.91</v>
+        <v>725.63</v>
       </c>
       <c r="C16" t="n">
-        <v>298.72</v>
+        <v>581.7</v>
       </c>
       <c r="D16" t="n">
-        <v>5.42</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +695,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1604.9</v>
+        <v>925.92</v>
       </c>
       <c r="C17" t="n">
-        <v>1450.73</v>
+        <v>820.5599999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>28.17</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +711,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>116.29</v>
+        <v>160.16</v>
       </c>
       <c r="C18" t="n">
-        <v>99.44</v>
+        <v>136.55</v>
       </c>
       <c r="D18" t="n">
-        <v>20.29</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +727,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>830.33</v>
+        <v>674.73</v>
       </c>
       <c r="C19" t="n">
-        <v>719.65</v>
+        <v>601.5</v>
       </c>
       <c r="D19" t="n">
-        <v>17.22</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +743,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>276.16</v>
+        <v>228.81</v>
       </c>
       <c r="C20" t="n">
-        <v>237.25</v>
+        <v>170.82</v>
       </c>
       <c r="D20" t="n">
-        <v>8.93</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +759,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3778.21</v>
+        <v>3546.6</v>
       </c>
       <c r="C21" t="n">
-        <v>2622.99</v>
+        <v>2420.04</v>
       </c>
       <c r="D21" t="n">
-        <v>19.54</v>
+        <v>16.2</v>
       </c>
     </row>
   </sheetData>
